--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486870_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486870_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4885</v>
+        <v>2.1053</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8976</v>
+        <v>0.7936</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5909</v>
+        <v>1.3117</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5991</v>
+        <v>2.0587</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1312</v>
+        <v>1.6349</v>
       </c>
       <c r="I2" t="n">
-        <v>2.468</v>
+        <v>0.4238</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2216</v>
+        <v>1.5868</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7092</v>
+        <v>1.35</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5124</v>
+        <v>0.2368</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6224</v>
+        <v>0.4719</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.578</v>
+        <v>0.2849</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0445</v>
+        <v>0.187</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.6694</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.1068</v>
+        <v>-2.0534</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5588</v>
+        <v>-0.9472</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2171</v>
+        <v>-0.5077</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7759</v>
+        <v>-0.4396</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.2259</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7709</v>
+        <v>2.0472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5185999999999999</v>
+        <v>2.3734</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2524</v>
+        <v>-0.3262</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0587</v>
+        <v>3.4979</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6349</v>
+        <v>-0.4092</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4238</v>
+        <v>3.9071</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5868</v>
+        <v>4.1441</v>
       </c>
       <c r="K3" t="n">
-        <v>1.35</v>
+        <v>0.4477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2368</v>
+        <v>3.6964</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4719</v>
+        <v>-0.6462</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2849</v>
+        <v>-0.8569</v>
       </c>
       <c r="O3" t="n">
-        <v>0.187</v>
+        <v>0.2107</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2816</v>
+        <v>-0.4775</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7827</v>
+        <v>-0.744</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4988</v>
+        <v>0.2665</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2259</v>
+        <v>-1.1786</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4579</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7285</v>
+        <v>2.0034</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2029</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4744</v>
+        <v>1.3537</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4979</v>
+        <v>4.5991</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4092</v>
+        <v>2.1312</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9071</v>
+        <v>2.468</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1441</v>
+        <v>5.2216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4477</v>
+        <v>2.7092</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6964</v>
+        <v>2.5124</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6462</v>
+        <v>-0.6224</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8569</v>
+        <v>-0.578</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2107</v>
+        <v>-0.0445</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2053</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7962</v>
+        <v>0.0737</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9145</v>
+        <v>-0.4651</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1183</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1499</v>
+        <v>0.3731</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8061</v>
+        <v>1.9107</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6562</v>
+        <v>-1.5377</v>
       </c>
       <c r="G5" t="n">
         <v>0.9426</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7927</v>
+        <v>-0.5696</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6587</v>
+        <v>-0.5541</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.134</v>
+        <v>-0.0155</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8233</v>
+        <v>-0.4593</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7978</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0255</v>
+        <v>0.0634</v>
       </c>
       <c r="G6" t="n">
         <v>0.5857</v>
@@ -922,13 +922,13 @@
         <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8197</v>
+        <v>-1.4557</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5732</v>
+        <v>-1.2981</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2465</v>
+        <v>-0.1576</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7597</v>
+        <v>-2.0095</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5679</v>
+        <v>-0.3242</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8081</v>
+        <v>-1.6853</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3447</v>
+        <v>-1.0835</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6869</v>
+        <v>-0.6781</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3422</v>
+        <v>-0.4054</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3163</v>
+        <v>-0.658</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3558</v>
+        <v>-0.4603</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0395</v>
+        <v>-0.1977</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0284</v>
+        <v>-0.4254</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3311</v>
+        <v>-0.2177</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3027</v>
+        <v>-0.2077</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.616</v>
+        <v>0.616</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.201</v>
+        <v>-1.3018</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2249</v>
+        <v>-0.8447</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4259</v>
+        <v>-0.457</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3372</v>
+        <v>-2.2078</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5334</v>
+        <v>-2.9863</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8039</v>
+        <v>0.7785</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0835</v>
+        <v>-1.3447</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6781</v>
+        <v>-1.6869</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4054</v>
+        <v>0.3422</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.658</v>
+        <v>-1.3163</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4603</v>
+        <v>-1.3558</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1977</v>
+        <v>0.0395</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4254</v>
+        <v>-0.0284</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2177</v>
+        <v>-0.3311</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2077</v>
+        <v>0.3027</v>
       </c>
       <c r="P8" t="n">
-        <v>0.616</v>
+        <v>-0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6296</v>
+        <v>-0.247</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.054</v>
+        <v>-0.6433</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5756</v>
+        <v>0.3962</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1781</v>
+        <v>-2.9936</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4767</v>
+        <v>-2.4108</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7014</v>
+        <v>-0.5828</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7992</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9477</v>
+        <v>-0.7632</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6587</v>
+        <v>-0.5928</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2889</v>
+        <v>-0.1704</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6366</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7245</v>
+        <v>-4.0489</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1628</v>
+        <v>-3.9536</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4383</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1365</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6229</v>
+        <v>-0.9472</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0462</v>
+        <v>-0.837</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4234</v>
+        <v>-0.1102</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9384</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3802</v>
+        <v>-4.5458</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1178</v>
+        <v>-2.4316</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2624</v>
+        <v>-2.1142</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3972</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.9967</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6201</v>
+        <v>-0.9339</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.211</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.0652</v>
+        <v>-9.735899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.231199999999999</v>
+        <v>-6.9018</v>
       </c>
       <c r="F12" t="n">
         <v>-2.8341</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9229</v>
+        <v>3.922899999999998</v>
       </c>
       <c r="H12" t="n">
         <v>-5.1273</v>
@@ -1363,10 +1363,10 @@
         <v>9.0504</v>
       </c>
       <c r="J12" t="n">
-        <v>9.281199999999998</v>
+        <v>9.281200000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2460000000000009</v>
+        <v>0.2459999999999996</v>
       </c>
       <c r="L12" t="n">
         <v>9.035200000000001</v>
@@ -1378,7 +1378,7 @@
         <v>-5.3733</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01519999999999999</v>
+        <v>0.0152000000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-3.0802</v>
@@ -1390,13 +1390,13 @@
         <v>9.240399999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.9617</v>
+        <v>-7.6322</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.7501</v>
+        <v>-7.4207</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2113</v>
+        <v>-0.2116</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9465</v>
@@ -1405,7 +1405,7 @@
         <v>3.558300000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.505</v>
+        <v>-6.505000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.8214</v>
+        <v>6.0228</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0682</v>
+        <v>4.5452</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7531</v>
+        <v>1.4776</v>
       </c>
       <c r="G13" t="n">
         <v>2.6277</v>
@@ -1468,13 +1468,13 @@
         <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8035</v>
+        <v>2.0049</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1776</v>
+        <v>0.6546</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6259</v>
+        <v>1.3504</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4579</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1808</v>
+        <v>5.777</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7084</v>
+        <v>3.1268</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4723</v>
+        <v>2.6502</v>
       </c>
       <c r="G14" t="n">
         <v>0.0277</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>0.537</v>
+        <v>1.1332</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.2675</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2229</v>
+        <v>1.4008</v>
       </c>
       <c r="V14" t="n">
         <v>2.3573</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8288</v>
+        <v>5.6385</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9378</v>
+        <v>3.193</v>
       </c>
       <c r="F15" t="n">
-        <v>1.891</v>
+        <v>2.4455</v>
       </c>
       <c r="G15" t="n">
         <v>0.6727</v>
@@ -1624,13 +1624,13 @@
         <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7269</v>
+        <v>1.0828</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6391</v>
+        <v>-0.3838</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9122</v>
+        <v>1.4667</v>
       </c>
       <c r="V15" t="n">
         <v>1.4189</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0732</v>
+        <v>0.1325</v>
       </c>
       <c r="E16" t="n">
         <v>-0.1192</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1924</v>
+        <v>0.2517</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0213</v>
@@ -1702,13 +1702,13 @@
         <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1581</v>
+        <v>-0.0988</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1976</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V16" t="n">
         <v>1.0472</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0731</v>
+        <v>-0.8935</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.747</v>
+        <v>-1.5255</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6739</v>
+        <v>0.632</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9707</v>
+        <v>-3.3934</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4655</v>
+        <v>-0.5438</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.4362</v>
+        <v>-2.8496</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2487</v>
+        <v>-2.2974</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4595</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.2108</v>
+        <v>-1.5529</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2194</v>
+        <v>-1.096</v>
       </c>
       <c r="N17" t="n">
-        <v>0.006</v>
+        <v>0.2007</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2254</v>
+        <v>-1.2966</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1297</v>
+        <v>1.4732</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0845</v>
+        <v>0.0307</v>
       </c>
       <c r="U17" t="n">
-        <v>2.0452</v>
+        <v>1.4425</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3311</v>
+        <v>-1.0216</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7347</v>
+        <v>-2.4792</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4036</v>
+        <v>1.4576</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.3934</v>
+        <v>-1.9707</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5438</v>
+        <v>2.4655</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8496</v>
+        <v>-4.4362</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.2974</v>
+        <v>0.2487</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7445000000000001</v>
+        <v>2.4595</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5529</v>
+        <v>-2.2108</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.096</v>
+        <v>-2.2194</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2007</v>
+        <v>0.006</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2966</v>
+        <v>-2.2254</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0356</v>
+        <v>2.1812</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1785</v>
+        <v>0.3522</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2141</v>
+        <v>1.829</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.608</v>
+        <v>-1.8765</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.854</v>
+        <v>-2.0632</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2461</v>
+        <v>0.1868</v>
       </c>
       <c r="G19" t="n">
         <v>0.8849</v>
@@ -1936,13 +1936,13 @@
         <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5688</v>
+        <v>0.3003</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0386</v>
+        <v>-0.1706</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5301</v>
+        <v>0.4709</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4189</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8266</v>
+        <v>-3.0166</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4254</v>
+        <v>-1.8438</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4012</v>
+        <v>-1.1728</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7506</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7721</v>
+        <v>0.5821</v>
       </c>
       <c r="T20" t="n">
-        <v>0.612</v>
+        <v>0.1936</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1601</v>
+        <v>0.3885</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>10.0654</v>
+        <v>10.7626</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8341</v>
+        <v>2.834100000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>7.231200000000001</v>
+        <v>7.928599999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-3.923000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>12.3206</v>
       </c>
       <c r="S21" t="n">
-        <v>7.9617</v>
+        <v>8.658899999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2115</v>
+        <v>0.2116000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>7.749999999999999</v>
+        <v>8.4476</v>
       </c>
       <c r="V21" t="n">
         <v>2.9466</v>
